--- a/Result/profitability/5512.xlsx
+++ b/Result/profitability/5512.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0375</v>
+        <v>0.03875</v>
       </c>
       <c r="N2" t="n">
-        <v>20.585</v>
+        <v>22.49</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04375</v>
+        <v>0.03375</v>
       </c>
       <c r="N3" t="n">
-        <v>22.00625</v>
+        <v>23.04625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -901,10 +901,10 @@
         <v>0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>0.055</v>
+        <v>0.0475</v>
       </c>
       <c r="N4" t="n">
-        <v>22.68</v>
+        <v>22.93375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1023,7 +1023,7 @@
         <v>0.0775</v>
       </c>
       <c r="N5" t="n">
-        <v>22.4275</v>
+        <v>22.87125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1139,10 +1139,10 @@
         <v>0.16</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09625</v>
+        <v>0.1025</v>
       </c>
       <c r="N6" t="n">
-        <v>22.00125</v>
+        <v>23.35625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1268,10 +1268,10 @@
         <v>0.38</v>
       </c>
       <c r="M7" t="n">
-        <v>0.14875</v>
+        <v>0.135</v>
       </c>
       <c r="N7" t="n">
-        <v>23.4825</v>
+        <v>23.78625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1395,10 +1395,10 @@
         <v>0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0.165</v>
+        <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>24.1</v>
+        <v>24.195</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1522,7 +1522,7 @@
         <v>1.17</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3049999999999999</v>
+        <v>0.305</v>
       </c>
       <c r="N9" t="n">
         <v>26.05</v>
@@ -2030,7 +2030,7 @@
         <v>0.77</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5399999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="N13" t="n">
         <v>34.91875</v>
@@ -9358,11 +9358,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>11.76%</t>
+          <t>11.78%</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="J71" t="n">
         <v>81</v>
@@ -9485,11 +9485,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>7.58%</t>
+          <t>7.56%</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>-91</v>
+        <v>-90</v>
       </c>
       <c r="J72" t="n">
         <v>43</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5512</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1282</v>
+      </c>
+      <c r="D75" t="n">
+        <v>949</v>
+      </c>
+      <c r="E75" t="n">
+        <v>333</v>
+      </c>
+      <c r="F75" t="n">
+        <v>25.96</v>
+      </c>
+      <c r="G75" t="n">
+        <v>207</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>16.13%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-52</v>
+      </c>
+      <c r="J75" t="n">
+        <v>155</v>
+      </c>
+      <c r="K75" t="n">
+        <v>7</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.03875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20.56375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.7600000000000016</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.03015873015873027</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.550000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1584114234716645</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
